--- a/output/yearly_population_iteration_46_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_46_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5074</v>
+        <v>7326</v>
       </c>
       <c r="C2" t="n">
-        <v>6925</v>
+        <v>6378</v>
       </c>
       <c r="D2" t="n">
-        <v>31535</v>
+        <v>34553</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3751</v>
+        <v>3941</v>
       </c>
       <c r="C3" t="n">
-        <v>4098</v>
+        <v>5495</v>
       </c>
       <c r="D3" t="n">
-        <v>14369</v>
+        <v>14972</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3101</v>
+        <v>3238</v>
       </c>
       <c r="C4" t="n">
-        <v>5020</v>
+        <v>7000</v>
       </c>
       <c r="D4" t="n">
-        <v>8111</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1918</v>
+        <v>2003</v>
       </c>
       <c r="C5" t="n">
-        <v>4022</v>
+        <v>5193</v>
       </c>
       <c r="D5" t="n">
-        <v>3262</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="C6" t="n">
-        <v>2496</v>
+        <v>2637</v>
       </c>
       <c r="D6" t="n">
-        <v>1302</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="C7" t="n">
-        <v>1486</v>
+        <v>1175</v>
       </c>
       <c r="D7" t="n">
-        <v>683</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C8" t="n">
-        <v>738</v>
+        <v>527</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>338</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5965</v>
+        <v>8634</v>
       </c>
       <c r="C2" t="n">
-        <v>6351</v>
+        <v>7354</v>
       </c>
       <c r="D2" t="n">
-        <v>27035</v>
+        <v>28256</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3558</v>
+        <v>4409</v>
       </c>
       <c r="C3" t="n">
-        <v>4737</v>
+        <v>5187</v>
       </c>
       <c r="D3" t="n">
-        <v>15737</v>
+        <v>16628</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2901</v>
+        <v>3037</v>
       </c>
       <c r="C4" t="n">
-        <v>4424</v>
+        <v>6117</v>
       </c>
       <c r="D4" t="n">
-        <v>8807</v>
+        <v>7606</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2164</v>
+        <v>2241</v>
       </c>
       <c r="C5" t="n">
-        <v>4407</v>
+        <v>5885</v>
       </c>
       <c r="D5" t="n">
-        <v>3954</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1312</v>
+        <v>1359</v>
       </c>
       <c r="C6" t="n">
-        <v>3135</v>
+        <v>3788</v>
       </c>
       <c r="D6" t="n">
-        <v>1572</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="C7" t="n">
-        <v>1940</v>
+        <v>1822</v>
       </c>
       <c r="D7" t="n">
-        <v>773</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C8" t="n">
-        <v>1053</v>
+        <v>812</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>506</v>
+        <v>386</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
         <v>249</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7532</v>
+        <v>9988</v>
       </c>
       <c r="C2" t="n">
-        <v>12700</v>
+        <v>13860</v>
       </c>
       <c r="D2" t="n">
-        <v>36655</v>
+        <v>41619</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3710</v>
+        <v>5022</v>
       </c>
       <c r="C3" t="n">
-        <v>4792</v>
+        <v>5395</v>
       </c>
       <c r="D3" t="n">
-        <v>16150</v>
+        <v>17025</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2739</v>
+        <v>3057</v>
       </c>
       <c r="C4" t="n">
-        <v>4427</v>
+        <v>5520</v>
       </c>
       <c r="D4" t="n">
-        <v>9603</v>
+        <v>8760</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2194</v>
+        <v>2282</v>
       </c>
       <c r="C5" t="n">
-        <v>4280</v>
+        <v>5862</v>
       </c>
       <c r="D5" t="n">
-        <v>4494</v>
+        <v>3415</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1507</v>
+        <v>1561</v>
       </c>
       <c r="C6" t="n">
-        <v>3643</v>
+        <v>4582</v>
       </c>
       <c r="D6" t="n">
-        <v>1894</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="C7" t="n">
-        <v>2412</v>
+        <v>2612</v>
       </c>
       <c r="D7" t="n">
-        <v>867</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C8" t="n">
-        <v>1408</v>
+        <v>1217</v>
       </c>
       <c r="D8" t="n">
-        <v>499</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C9" t="n">
-        <v>709</v>
+        <v>544</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>292</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
         <v>128</v>
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6825</v>
+        <v>9071</v>
       </c>
       <c r="C2" t="n">
-        <v>8534</v>
+        <v>9424</v>
       </c>
       <c r="D2" t="n">
-        <v>29944</v>
+        <v>33948</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4704</v>
+        <v>5813</v>
       </c>
       <c r="C3" t="n">
-        <v>8010</v>
+        <v>9068</v>
       </c>
       <c r="D3" t="n">
-        <v>17741</v>
+        <v>18381</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2027</v>
+        <v>2108</v>
       </c>
       <c r="C4" t="n">
-        <v>6573</v>
+        <v>8701</v>
       </c>
       <c r="D4" t="n">
-        <v>9424</v>
+        <v>8078</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1392</v>
+        <v>1442</v>
       </c>
       <c r="C5" t="n">
-        <v>3570</v>
+        <v>4490</v>
       </c>
       <c r="D5" t="n">
-        <v>3107</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="C6" t="n">
-        <v>2363</v>
+        <v>2559</v>
       </c>
       <c r="D6" t="n">
-        <v>849</v>
+        <v>728</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C7" t="n">
-        <v>1379</v>
+        <v>1192</v>
       </c>
       <c r="D7" t="n">
-        <v>489</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C8" t="n">
-        <v>694</v>
+        <v>533</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
         <v>125</v>
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4297</v>
+        <v>5265</v>
       </c>
       <c r="C2" t="n">
-        <v>3527</v>
+        <v>4077</v>
       </c>
       <c r="D2" t="n">
-        <v>20900</v>
+        <v>23559</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4843</v>
+        <v>6194</v>
       </c>
       <c r="C3" t="n">
-        <v>7471</v>
+        <v>8360</v>
       </c>
       <c r="D3" t="n">
-        <v>18378</v>
+        <v>19439</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2680</v>
+        <v>3080</v>
       </c>
       <c r="C4" t="n">
-        <v>7301</v>
+        <v>9026</v>
       </c>
       <c r="D4" t="n">
-        <v>10595</v>
+        <v>9570</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1555</v>
+        <v>1594</v>
       </c>
       <c r="C5" t="n">
-        <v>4935</v>
+        <v>6350</v>
       </c>
       <c r="D5" t="n">
-        <v>3860</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="C6" t="n">
-        <v>2935</v>
+        <v>3357</v>
       </c>
       <c r="D6" t="n">
-        <v>1080</v>
+        <v>890</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C7" t="n">
-        <v>1756</v>
+        <v>1671</v>
       </c>
       <c r="D7" t="n">
-        <v>537</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>919</v>
+        <v>719</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>394</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
+        <v>169</v>
+      </c>
+      <c r="D11" t="n">
         <v>168</v>
-      </c>
-      <c r="D11" t="n">
-        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4260</v>
+        <v>5031</v>
       </c>
       <c r="C2" t="n">
-        <v>6570</v>
+        <v>4900</v>
       </c>
       <c r="D2" t="n">
-        <v>22014</v>
+        <v>20820</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3871</v>
+        <v>4871</v>
       </c>
       <c r="C3" t="n">
-        <v>4938</v>
+        <v>5628</v>
       </c>
       <c r="D3" t="n">
-        <v>17653</v>
+        <v>18881</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3125</v>
+        <v>3817</v>
       </c>
       <c r="C4" t="n">
-        <v>7234</v>
+        <v>8512</v>
       </c>
       <c r="D4" t="n">
-        <v>11441</v>
+        <v>10889</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1810</v>
+        <v>1966</v>
       </c>
       <c r="C5" t="n">
-        <v>6015</v>
+        <v>7476</v>
       </c>
       <c r="D5" t="n">
-        <v>4841</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1095</v>
+        <v>1115</v>
       </c>
       <c r="C6" t="n">
-        <v>3808</v>
+        <v>4707</v>
       </c>
       <c r="D6" t="n">
-        <v>1492</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C7" t="n">
-        <v>2292</v>
+        <v>2413</v>
       </c>
       <c r="D7" t="n">
-        <v>616</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C8" t="n">
-        <v>1272</v>
+        <v>1108</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>598</v>
+        <v>481</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2467,7 +2467,7 @@
         <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
         <v>134</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>64</v>
@@ -2537,7 +2537,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2579,7 +2579,7 @@
         <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2526</v>
+        <v>3007</v>
       </c>
       <c r="C2" t="n">
-        <v>3033</v>
+        <v>2309</v>
       </c>
       <c r="D2" t="n">
-        <v>15189</v>
+        <v>14514</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3858</v>
+        <v>4736</v>
       </c>
       <c r="C3" t="n">
-        <v>5341</v>
+        <v>5212</v>
       </c>
       <c r="D3" t="n">
-        <v>17717</v>
+        <v>18659</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3441</v>
+        <v>4196</v>
       </c>
       <c r="C4" t="n">
-        <v>7006</v>
+        <v>8210</v>
       </c>
       <c r="D4" t="n">
-        <v>12285</v>
+        <v>11808</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1911</v>
+        <v>2030</v>
       </c>
       <c r="C5" t="n">
-        <v>7211</v>
+        <v>8774</v>
       </c>
       <c r="D5" t="n">
-        <v>5201</v>
+        <v>4154</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="C6" t="n">
-        <v>4610</v>
+        <v>5569</v>
       </c>
       <c r="D6" t="n">
-        <v>1446</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>2375</v>
+        <v>2357</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>984</v>
+        <v>807</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2764,7 +2764,7 @@
         <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
         <v>131</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -2834,7 +2834,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2876,7 +2876,7 @@
         <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3097</v>
+        <v>3676</v>
       </c>
       <c r="C2" t="n">
-        <v>4254</v>
+        <v>2227</v>
       </c>
       <c r="D2" t="n">
-        <v>16351</v>
+        <v>14564</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2820</v>
+        <v>3447</v>
       </c>
       <c r="C3" t="n">
-        <v>3801</v>
+        <v>3475</v>
       </c>
       <c r="D3" t="n">
-        <v>16182</v>
+        <v>17020</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3191</v>
+        <v>3861</v>
       </c>
       <c r="C4" t="n">
-        <v>6128</v>
+        <v>6707</v>
       </c>
       <c r="D4" t="n">
-        <v>12798</v>
+        <v>12501</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2256</v>
+        <v>2562</v>
       </c>
       <c r="C5" t="n">
-        <v>6968</v>
+        <v>8342</v>
       </c>
       <c r="D5" t="n">
-        <v>6180</v>
+        <v>5129</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1181</v>
+        <v>1223</v>
       </c>
       <c r="C6" t="n">
-        <v>5780</v>
+        <v>6980</v>
       </c>
       <c r="D6" t="n">
-        <v>1931</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C7" t="n">
-        <v>3295</v>
+        <v>3638</v>
       </c>
       <c r="D7" t="n">
-        <v>716</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1530</v>
+        <v>1384</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>513</v>
+        <v>443</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2367</v>
+        <v>2685</v>
       </c>
       <c r="C2" t="n">
-        <v>2108</v>
+        <v>1924</v>
       </c>
       <c r="D2" t="n">
-        <v>12799</v>
+        <v>10665</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2549</v>
+        <v>3085</v>
       </c>
       <c r="C3" t="n">
-        <v>3645</v>
+        <v>2718</v>
       </c>
       <c r="D3" t="n">
-        <v>15321</v>
+        <v>15799</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2838</v>
+        <v>3446</v>
       </c>
       <c r="C4" t="n">
-        <v>5216</v>
+        <v>5457</v>
       </c>
       <c r="D4" t="n">
-        <v>12986</v>
+        <v>12968</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2438</v>
+        <v>2783</v>
       </c>
       <c r="C5" t="n">
-        <v>6717</v>
+        <v>7827</v>
       </c>
       <c r="D5" t="n">
-        <v>6873</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1374</v>
+        <v>1463</v>
       </c>
       <c r="C6" t="n">
-        <v>6399</v>
+        <v>7692</v>
       </c>
       <c r="D6" t="n">
-        <v>2312</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="C7" t="n">
-        <v>4152</v>
+        <v>4704</v>
       </c>
       <c r="D7" t="n">
-        <v>816</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>1993</v>
+        <v>1894</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>602</v>
+        <v>512</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3915</v>
+        <v>4583</v>
       </c>
       <c r="C2" t="n">
-        <v>7212</v>
+        <v>5327</v>
       </c>
       <c r="D2" t="n">
-        <v>21051</v>
+        <v>22315</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2090</v>
+        <v>2476</v>
       </c>
       <c r="C3" t="n">
-        <v>2683</v>
+        <v>2138</v>
       </c>
       <c r="D3" t="n">
-        <v>14037</v>
+        <v>14171</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2377</v>
+        <v>2913</v>
       </c>
       <c r="C4" t="n">
-        <v>4428</v>
+        <v>4186</v>
       </c>
       <c r="D4" t="n">
-        <v>12927</v>
+        <v>12981</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2353</v>
+        <v>2743</v>
       </c>
       <c r="C5" t="n">
-        <v>5957</v>
+        <v>6708</v>
       </c>
       <c r="D5" t="n">
-        <v>7419</v>
+        <v>6587</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1622</v>
+        <v>1770</v>
       </c>
       <c r="C6" t="n">
-        <v>6469</v>
+        <v>7679</v>
       </c>
       <c r="D6" t="n">
-        <v>2894</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C7" t="n">
-        <v>5049</v>
+        <v>5860</v>
       </c>
       <c r="D7" t="n">
-        <v>998</v>
+        <v>842</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>2753</v>
+        <v>2857</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>1071</v>
+        <v>963</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>343</v>
+        <v>307</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
         <v>95</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6229</v>
+        <v>5776</v>
       </c>
       <c r="C2" t="n">
-        <v>5420</v>
+        <v>3738</v>
       </c>
       <c r="D2" t="n">
-        <v>14421</v>
+        <v>4145</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2801</v>
+        <v>3315</v>
       </c>
       <c r="C2" t="n">
-        <v>4096</v>
+        <v>3068</v>
       </c>
       <c r="D2" t="n">
-        <v>15493</v>
+        <v>16602</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2874</v>
+        <v>3419</v>
       </c>
       <c r="C3" t="n">
-        <v>3965</v>
+        <v>3040</v>
       </c>
       <c r="D3" t="n">
-        <v>15691</v>
+        <v>15726</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3384</v>
+        <v>4022</v>
       </c>
       <c r="C4" t="n">
-        <v>6364</v>
+        <v>6348</v>
       </c>
       <c r="D4" t="n">
-        <v>13250</v>
+        <v>13170</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1563</v>
+        <v>1686</v>
       </c>
       <c r="C5" t="n">
-        <v>8897</v>
+        <v>10410</v>
       </c>
       <c r="D5" t="n">
-        <v>6830</v>
+        <v>5895</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C6" t="n">
-        <v>6279</v>
+        <v>7172</v>
       </c>
       <c r="D6" t="n">
-        <v>2268</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>2697</v>
+        <v>2799</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>1049</v>
+        <v>943</v>
       </c>
       <c r="D8" t="n">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
         <v>93</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7213</v>
+        <v>6723</v>
       </c>
       <c r="C2" t="n">
-        <v>5813</v>
+        <v>2842</v>
       </c>
       <c r="D2" t="n">
-        <v>25344</v>
+        <v>11940</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2646</v>
+        <v>2454</v>
       </c>
       <c r="C3" t="n">
-        <v>2731</v>
+        <v>1913</v>
       </c>
       <c r="D3" t="n">
-        <v>3062</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5099</v>
+        <v>4480</v>
       </c>
       <c r="C2" t="n">
-        <v>4661</v>
+        <v>2663</v>
       </c>
       <c r="D2" t="n">
-        <v>26706</v>
+        <v>13142</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4047</v>
+        <v>3821</v>
       </c>
       <c r="C3" t="n">
-        <v>3859</v>
+        <v>2107</v>
       </c>
       <c r="D3" t="n">
-        <v>6580</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1184</v>
+        <v>1099</v>
       </c>
       <c r="C4" t="n">
-        <v>1645</v>
+        <v>1182</v>
       </c>
       <c r="D4" t="n">
-        <v>1798</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5303</v>
+        <v>4517</v>
       </c>
       <c r="C2" t="n">
-        <v>4112</v>
+        <v>9310</v>
       </c>
       <c r="D2" t="n">
-        <v>22787</v>
+        <v>19387</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3757</v>
+        <v>3419</v>
       </c>
       <c r="C3" t="n">
-        <v>3718</v>
+        <v>2087</v>
       </c>
       <c r="D3" t="n">
-        <v>9326</v>
+        <v>4439</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2224</v>
+        <v>2114</v>
       </c>
       <c r="C4" t="n">
-        <v>2864</v>
+        <v>1690</v>
       </c>
       <c r="D4" t="n">
-        <v>2661</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>536</v>
+        <v>510</v>
       </c>
       <c r="C5" t="n">
-        <v>996</v>
+        <v>751</v>
       </c>
       <c r="D5" t="n">
-        <v>1259</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>116</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5238</v>
+        <v>7453</v>
       </c>
       <c r="C2" t="n">
-        <v>8073</v>
+        <v>9814</v>
       </c>
       <c r="D2" t="n">
-        <v>28872</v>
+        <v>22243</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3690</v>
+        <v>3249</v>
       </c>
       <c r="C3" t="n">
-        <v>3412</v>
+        <v>5106</v>
       </c>
       <c r="D3" t="n">
-        <v>10715</v>
+        <v>6398</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2546</v>
+        <v>2370</v>
       </c>
       <c r="C4" t="n">
-        <v>3263</v>
+        <v>1855</v>
       </c>
       <c r="D4" t="n">
-        <v>3795</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1130</v>
+        <v>1087</v>
       </c>
       <c r="C5" t="n">
-        <v>1934</v>
+        <v>1240</v>
       </c>
       <c r="D5" t="n">
-        <v>1450</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C6" t="n">
-        <v>652</v>
+        <v>531</v>
       </c>
       <c r="D6" t="n">
-        <v>956</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7790</v>
+        <v>6740</v>
       </c>
       <c r="C2" t="n">
-        <v>8740</v>
+        <v>11762</v>
       </c>
       <c r="D2" t="n">
-        <v>25430</v>
+        <v>31438</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3232</v>
+        <v>3920</v>
       </c>
       <c r="C3" t="n">
-        <v>4746</v>
+        <v>6221</v>
       </c>
       <c r="D3" t="n">
-        <v>11967</v>
+        <v>8037</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1923</v>
+        <v>1743</v>
       </c>
       <c r="C4" t="n">
-        <v>2739</v>
+        <v>3047</v>
       </c>
       <c r="D4" t="n">
-        <v>4311</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>963</v>
+        <v>909</v>
       </c>
       <c r="C5" t="n">
-        <v>1902</v>
+        <v>1148</v>
       </c>
       <c r="D5" t="n">
-        <v>1455</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C6" t="n">
-        <v>874</v>
+        <v>600</v>
       </c>
       <c r="D6" t="n">
-        <v>791</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>317</v>
+        <v>282</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6022</v>
+        <v>6989</v>
       </c>
       <c r="C2" t="n">
-        <v>5802</v>
+        <v>9052</v>
       </c>
       <c r="D2" t="n">
-        <v>25576</v>
+        <v>32939</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4597</v>
+        <v>4448</v>
       </c>
       <c r="C3" t="n">
-        <v>6160</v>
+        <v>8206</v>
       </c>
       <c r="D3" t="n">
-        <v>13348</v>
+        <v>11551</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2262</v>
+        <v>2516</v>
       </c>
       <c r="C4" t="n">
-        <v>3869</v>
+        <v>4964</v>
       </c>
       <c r="D4" t="n">
-        <v>5682</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1280</v>
+        <v>1183</v>
       </c>
       <c r="C5" t="n">
-        <v>2360</v>
+        <v>2272</v>
       </c>
       <c r="D5" t="n">
-        <v>1986</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="C6" t="n">
-        <v>1455</v>
+        <v>913</v>
       </c>
       <c r="D6" t="n">
-        <v>899</v>
+        <v>811</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C7" t="n">
-        <v>633</v>
+        <v>465</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4746</v>
+        <v>4848</v>
       </c>
       <c r="C2" t="n">
-        <v>4245</v>
+        <v>5200</v>
       </c>
       <c r="D2" t="n">
-        <v>21159</v>
+        <v>26164</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4358</v>
+        <v>4690</v>
       </c>
       <c r="C3" t="n">
-        <v>5163</v>
+        <v>7496</v>
       </c>
       <c r="D3" t="n">
-        <v>14343</v>
+        <v>14141</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2921</v>
+        <v>2988</v>
       </c>
       <c r="C4" t="n">
-        <v>5086</v>
+        <v>6728</v>
       </c>
       <c r="D4" t="n">
-        <v>6981</v>
+        <v>4956</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1563</v>
+        <v>1629</v>
       </c>
       <c r="C5" t="n">
-        <v>3113</v>
+        <v>3701</v>
       </c>
       <c r="D5" t="n">
-        <v>2580</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>851</v>
+        <v>811</v>
       </c>
       <c r="C6" t="n">
-        <v>1924</v>
+        <v>1645</v>
       </c>
       <c r="D6" t="n">
-        <v>1084</v>
+        <v>888</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C7" t="n">
-        <v>1067</v>
+        <v>706</v>
       </c>
       <c r="D7" t="n">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>456</v>
+        <v>363</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_46_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_46_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7326</v>
+        <v>5445</v>
       </c>
       <c r="C2" t="n">
-        <v>6378</v>
+        <v>10111</v>
       </c>
       <c r="D2" t="n">
-        <v>34553</v>
+        <v>25382</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3941</v>
+        <v>3629</v>
       </c>
       <c r="C3" t="n">
-        <v>5495</v>
+        <v>9923</v>
       </c>
       <c r="D3" t="n">
-        <v>14972</v>
+        <v>13679</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3238</v>
+        <v>2658</v>
       </c>
       <c r="C4" t="n">
-        <v>7000</v>
+        <v>7199</v>
       </c>
       <c r="D4" t="n">
-        <v>6480</v>
+        <v>7017</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2003</v>
+        <v>1756</v>
       </c>
       <c r="C5" t="n">
-        <v>5193</v>
+        <v>5451</v>
       </c>
       <c r="D5" t="n">
-        <v>2216</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1081</v>
+        <v>1008</v>
       </c>
       <c r="C6" t="n">
-        <v>2637</v>
+        <v>3451</v>
       </c>
       <c r="D6" t="n">
-        <v>1020</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>502</v>
+        <v>458</v>
       </c>
       <c r="C7" t="n">
-        <v>1175</v>
+        <v>1984</v>
       </c>
       <c r="D7" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>527</v>
+        <v>907</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8634</v>
+        <v>6879</v>
       </c>
       <c r="C2" t="n">
-        <v>7354</v>
+        <v>7793</v>
       </c>
       <c r="D2" t="n">
-        <v>28256</v>
+        <v>31717</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4409</v>
+        <v>3597</v>
       </c>
       <c r="C3" t="n">
-        <v>5187</v>
+        <v>8836</v>
       </c>
       <c r="D3" t="n">
-        <v>16628</v>
+        <v>14279</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3037</v>
+        <v>2618</v>
       </c>
       <c r="C4" t="n">
-        <v>6117</v>
+        <v>8235</v>
       </c>
       <c r="D4" t="n">
-        <v>7606</v>
+        <v>7759</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2241</v>
+        <v>1889</v>
       </c>
       <c r="C5" t="n">
-        <v>5885</v>
+        <v>6126</v>
       </c>
       <c r="D5" t="n">
-        <v>2844</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1359</v>
+        <v>1212</v>
       </c>
       <c r="C6" t="n">
-        <v>3788</v>
+        <v>4248</v>
       </c>
       <c r="D6" t="n">
-        <v>1180</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>671</v>
+        <v>610</v>
       </c>
       <c r="C7" t="n">
-        <v>1822</v>
+        <v>2596</v>
       </c>
       <c r="D7" t="n">
-        <v>690</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>287</v>
+        <v>252</v>
       </c>
       <c r="C8" t="n">
-        <v>812</v>
+        <v>1360</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>386</v>
+        <v>581</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
         <v>127</v>
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9988</v>
+        <v>8091</v>
       </c>
       <c r="C2" t="n">
-        <v>13860</v>
+        <v>9172</v>
       </c>
       <c r="D2" t="n">
-        <v>41619</v>
+        <v>33514</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5022</v>
+        <v>3942</v>
       </c>
       <c r="C3" t="n">
-        <v>5395</v>
+        <v>7493</v>
       </c>
       <c r="D3" t="n">
-        <v>17025</v>
+        <v>15457</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3057</v>
+        <v>2553</v>
       </c>
       <c r="C4" t="n">
-        <v>5520</v>
+        <v>8317</v>
       </c>
       <c r="D4" t="n">
-        <v>8760</v>
+        <v>8462</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2282</v>
+        <v>1932</v>
       </c>
       <c r="C5" t="n">
-        <v>5862</v>
+        <v>6790</v>
       </c>
       <c r="D5" t="n">
-        <v>3415</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1561</v>
+        <v>1343</v>
       </c>
       <c r="C6" t="n">
-        <v>4582</v>
+        <v>4909</v>
       </c>
       <c r="D6" t="n">
-        <v>1404</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>848</v>
+        <v>752</v>
       </c>
       <c r="C7" t="n">
-        <v>2612</v>
+        <v>3242</v>
       </c>
       <c r="D7" t="n">
-        <v>743</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="C8" t="n">
-        <v>1217</v>
+        <v>1806</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="C9" t="n">
-        <v>544</v>
+        <v>857</v>
       </c>
       <c r="D9" t="n">
         <v>334</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>292</v>
+        <v>382</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D11" t="n">
         <v>208</v>
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9071</v>
+        <v>7387</v>
       </c>
       <c r="C2" t="n">
-        <v>9424</v>
+        <v>6383</v>
       </c>
       <c r="D2" t="n">
-        <v>33948</v>
+        <v>27553</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5813</v>
+        <v>4626</v>
       </c>
       <c r="C3" t="n">
-        <v>9068</v>
+        <v>11740</v>
       </c>
       <c r="D3" t="n">
-        <v>18381</v>
+        <v>16696</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2108</v>
+        <v>1785</v>
       </c>
       <c r="C4" t="n">
-        <v>8701</v>
+        <v>10909</v>
       </c>
       <c r="D4" t="n">
-        <v>8078</v>
+        <v>8095</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1442</v>
+        <v>1240</v>
       </c>
       <c r="C5" t="n">
-        <v>4490</v>
+        <v>4810</v>
       </c>
       <c r="D5" t="n">
-        <v>2293</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>783</v>
+        <v>694</v>
       </c>
       <c r="C6" t="n">
-        <v>2559</v>
+        <v>3177</v>
       </c>
       <c r="D6" t="n">
-        <v>728</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>361</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>1192</v>
+        <v>1769</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>533</v>
+        <v>839</v>
       </c>
       <c r="D8" t="n">
         <v>327</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>374</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
         <v>203</v>
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
         <v>80</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5265</v>
+        <v>4362</v>
       </c>
       <c r="C2" t="n">
-        <v>4077</v>
+        <v>3352</v>
       </c>
       <c r="D2" t="n">
-        <v>23559</v>
+        <v>20249</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6194</v>
+        <v>4945</v>
       </c>
       <c r="C3" t="n">
-        <v>8360</v>
+        <v>8526</v>
       </c>
       <c r="D3" t="n">
-        <v>19439</v>
+        <v>17371</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3080</v>
+        <v>2456</v>
       </c>
       <c r="C4" t="n">
-        <v>9026</v>
+        <v>11475</v>
       </c>
       <c r="D4" t="n">
-        <v>9570</v>
+        <v>9165</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1594</v>
+        <v>1373</v>
       </c>
       <c r="C5" t="n">
-        <v>6350</v>
+        <v>7295</v>
       </c>
       <c r="D5" t="n">
-        <v>2989</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>946</v>
+        <v>813</v>
       </c>
       <c r="C6" t="n">
-        <v>3357</v>
+        <v>3920</v>
       </c>
       <c r="D6" t="n">
-        <v>890</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="C7" t="n">
-        <v>1671</v>
+        <v>2265</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>719</v>
+        <v>1116</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>407</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5031</v>
+        <v>4934</v>
       </c>
       <c r="C2" t="n">
-        <v>4900</v>
+        <v>4520</v>
       </c>
       <c r="D2" t="n">
-        <v>20820</v>
+        <v>27821</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4871</v>
+        <v>3958</v>
       </c>
       <c r="C3" t="n">
-        <v>5628</v>
+        <v>5515</v>
       </c>
       <c r="D3" t="n">
-        <v>18881</v>
+        <v>16595</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3817</v>
+        <v>3003</v>
       </c>
       <c r="C4" t="n">
-        <v>8512</v>
+        <v>9849</v>
       </c>
       <c r="D4" t="n">
-        <v>10889</v>
+        <v>10225</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1966</v>
+        <v>1611</v>
       </c>
       <c r="C5" t="n">
-        <v>7476</v>
+        <v>9029</v>
       </c>
       <c r="D5" t="n">
-        <v>3908</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1115</v>
+        <v>949</v>
       </c>
       <c r="C6" t="n">
-        <v>4707</v>
+        <v>5379</v>
       </c>
       <c r="D6" t="n">
-        <v>1180</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>510</v>
+        <v>431</v>
       </c>
       <c r="C7" t="n">
-        <v>2413</v>
+        <v>2945</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="C8" t="n">
-        <v>1108</v>
+        <v>1576</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>481</v>
+        <v>667</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>134</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3007</v>
+        <v>2976</v>
       </c>
       <c r="C2" t="n">
-        <v>2309</v>
+        <v>2197</v>
       </c>
       <c r="D2" t="n">
-        <v>14514</v>
+        <v>19429</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4736</v>
+        <v>4033</v>
       </c>
       <c r="C3" t="n">
-        <v>5212</v>
+        <v>5046</v>
       </c>
       <c r="D3" t="n">
-        <v>18659</v>
+        <v>17390</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4196</v>
+        <v>3290</v>
       </c>
       <c r="C4" t="n">
-        <v>8210</v>
+        <v>9258</v>
       </c>
       <c r="D4" t="n">
-        <v>11808</v>
+        <v>11032</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2030</v>
+        <v>1669</v>
       </c>
       <c r="C5" t="n">
-        <v>8774</v>
+        <v>10581</v>
       </c>
       <c r="D5" t="n">
-        <v>4154</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>924</v>
+        <v>766</v>
       </c>
       <c r="C6" t="n">
-        <v>5569</v>
+        <v>6230</v>
       </c>
       <c r="D6" t="n">
-        <v>1166</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>2357</v>
+        <v>3001</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>807</v>
+        <v>1101</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
         <v>131</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3676</v>
+        <v>2790</v>
       </c>
       <c r="C2" t="n">
-        <v>2227</v>
+        <v>5117</v>
       </c>
       <c r="D2" t="n">
-        <v>14564</v>
+        <v>18017</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3447</v>
+        <v>3093</v>
       </c>
       <c r="C3" t="n">
-        <v>3475</v>
+        <v>3411</v>
       </c>
       <c r="D3" t="n">
-        <v>17020</v>
+        <v>16510</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3861</v>
+        <v>3121</v>
       </c>
       <c r="C4" t="n">
-        <v>6707</v>
+        <v>7164</v>
       </c>
       <c r="D4" t="n">
-        <v>12501</v>
+        <v>11673</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2562</v>
+        <v>2032</v>
       </c>
       <c r="C5" t="n">
-        <v>8342</v>
+        <v>9890</v>
       </c>
       <c r="D5" t="n">
-        <v>5129</v>
+        <v>5081</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1223</v>
+        <v>993</v>
       </c>
       <c r="C6" t="n">
-        <v>6980</v>
+        <v>7990</v>
       </c>
       <c r="D6" t="n">
-        <v>1552</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>275</v>
       </c>
       <c r="C7" t="n">
-        <v>3638</v>
+        <v>4292</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1384</v>
+        <v>1773</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>443</v>
+        <v>538</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>57</v>
+      </c>
+      <c r="D13" t="n">
         <v>61</v>
-      </c>
-      <c r="D13" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>44</v>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
-      </c>
-      <c r="D14" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2685</v>
+        <v>2000</v>
       </c>
       <c r="C2" t="n">
-        <v>1924</v>
+        <v>2974</v>
       </c>
       <c r="D2" t="n">
-        <v>10665</v>
+        <v>14568</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3085</v>
+        <v>2633</v>
       </c>
       <c r="C3" t="n">
-        <v>2718</v>
+        <v>3724</v>
       </c>
       <c r="D3" t="n">
-        <v>15799</v>
+        <v>15807</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3446</v>
+        <v>2838</v>
       </c>
       <c r="C4" t="n">
-        <v>5457</v>
+        <v>5780</v>
       </c>
       <c r="D4" t="n">
-        <v>12968</v>
+        <v>12033</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2783</v>
+        <v>2229</v>
       </c>
       <c r="C5" t="n">
-        <v>7827</v>
+        <v>9053</v>
       </c>
       <c r="D5" t="n">
-        <v>5800</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1463</v>
+        <v>1149</v>
       </c>
       <c r="C6" t="n">
-        <v>7692</v>
+        <v>8877</v>
       </c>
       <c r="D6" t="n">
-        <v>1888</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>311</v>
+        <v>244</v>
       </c>
       <c r="C7" t="n">
-        <v>4704</v>
+        <v>5418</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1894</v>
+        <v>2305</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>512</v>
+        <v>597</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
         <v>179</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>126</v>
+      </c>
+      <c r="D11" t="n">
         <v>136</v>
-      </c>
-      <c r="D11" t="n">
-        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4583</v>
+        <v>2888</v>
       </c>
       <c r="C2" t="n">
-        <v>5327</v>
+        <v>17772</v>
       </c>
       <c r="D2" t="n">
-        <v>22315</v>
+        <v>17462</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2476</v>
+        <v>2040</v>
       </c>
       <c r="C3" t="n">
-        <v>2138</v>
+        <v>3072</v>
       </c>
       <c r="D3" t="n">
-        <v>14171</v>
+        <v>14681</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2913</v>
+        <v>2406</v>
       </c>
       <c r="C4" t="n">
-        <v>4186</v>
+        <v>4830</v>
       </c>
       <c r="D4" t="n">
-        <v>12981</v>
+        <v>12174</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2743</v>
+        <v>2236</v>
       </c>
       <c r="C5" t="n">
-        <v>6708</v>
+        <v>7607</v>
       </c>
       <c r="D5" t="n">
-        <v>6587</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1770</v>
+        <v>1372</v>
       </c>
       <c r="C6" t="n">
-        <v>7679</v>
+        <v>8870</v>
       </c>
       <c r="D6" t="n">
-        <v>2352</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>594</v>
+        <v>460</v>
       </c>
       <c r="C7" t="n">
-        <v>5860</v>
+        <v>6636</v>
       </c>
       <c r="D7" t="n">
-        <v>842</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>2857</v>
+        <v>3363</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>963</v>
+        <v>1115</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5776</v>
+        <v>4764</v>
       </c>
       <c r="C2" t="n">
-        <v>3738</v>
+        <v>6606</v>
       </c>
       <c r="D2" t="n">
-        <v>4145</v>
+        <v>6521</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3315</v>
+        <v>2111</v>
       </c>
       <c r="C2" t="n">
-        <v>3068</v>
+        <v>10521</v>
       </c>
       <c r="D2" t="n">
-        <v>16602</v>
+        <v>12992</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3419</v>
+        <v>2765</v>
       </c>
       <c r="C3" t="n">
-        <v>3040</v>
+        <v>6456</v>
       </c>
       <c r="D3" t="n">
-        <v>15726</v>
+        <v>16006</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4022</v>
+        <v>3275</v>
       </c>
       <c r="C4" t="n">
-        <v>6348</v>
+        <v>7382</v>
       </c>
       <c r="D4" t="n">
-        <v>13170</v>
+        <v>12259</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1686</v>
+        <v>1288</v>
       </c>
       <c r="C5" t="n">
-        <v>10410</v>
+        <v>11874</v>
       </c>
       <c r="D5" t="n">
-        <v>5895</v>
+        <v>5688</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>548</v>
+        <v>425</v>
       </c>
       <c r="C6" t="n">
-        <v>7172</v>
+        <v>8067</v>
       </c>
       <c r="D6" t="n">
-        <v>1870</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
-        <v>2799</v>
+        <v>3295</v>
       </c>
       <c r="D7" t="n">
-        <v>537</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>943</v>
+        <v>1092</v>
       </c>
       <c r="D8" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6723</v>
+        <v>7343</v>
       </c>
       <c r="C2" t="n">
-        <v>2842</v>
+        <v>8325</v>
       </c>
       <c r="D2" t="n">
-        <v>11940</v>
+        <v>17779</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2454</v>
+        <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>1913</v>
+        <v>3382</v>
       </c>
       <c r="D3" t="n">
-        <v>1368</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4480</v>
+        <v>4515</v>
       </c>
       <c r="C2" t="n">
-        <v>2663</v>
+        <v>5773</v>
       </c>
       <c r="D2" t="n">
-        <v>13142</v>
+        <v>15715</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3821</v>
+        <v>3841</v>
       </c>
       <c r="C3" t="n">
-        <v>2107</v>
+        <v>5328</v>
       </c>
       <c r="D3" t="n">
-        <v>3043</v>
+        <v>4301</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1099</v>
+        <v>913</v>
       </c>
       <c r="C4" t="n">
-        <v>1182</v>
+        <v>2024</v>
       </c>
       <c r="D4" t="n">
-        <v>1456</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
         <v>411</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4910,7 +4910,7 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
         <v>441</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4517</v>
+        <v>5153</v>
       </c>
       <c r="C2" t="n">
-        <v>9310</v>
+        <v>9049</v>
       </c>
       <c r="D2" t="n">
-        <v>19387</v>
+        <v>26251</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3419</v>
+        <v>3438</v>
       </c>
       <c r="C3" t="n">
-        <v>2087</v>
+        <v>4821</v>
       </c>
       <c r="D3" t="n">
-        <v>4439</v>
+        <v>5817</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2114</v>
+        <v>2008</v>
       </c>
       <c r="C4" t="n">
-        <v>1690</v>
+        <v>3853</v>
       </c>
       <c r="D4" t="n">
-        <v>1702</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="5">
@@ -5176,10 +5176,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>510</v>
+        <v>435</v>
       </c>
       <c r="C5" t="n">
-        <v>751</v>
+        <v>1202</v>
       </c>
       <c r="D5" t="n">
         <v>1201</v>
@@ -5193,7 +5193,7 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>625</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5274,7 +5274,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
         <v>148</v>
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7453</v>
+        <v>5908</v>
       </c>
       <c r="C2" t="n">
-        <v>9814</v>
+        <v>8184</v>
       </c>
       <c r="D2" t="n">
-        <v>22243</v>
+        <v>30378</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3249</v>
+        <v>3489</v>
       </c>
       <c r="C3" t="n">
-        <v>5106</v>
+        <v>6090</v>
       </c>
       <c r="D3" t="n">
-        <v>6398</v>
+        <v>8513</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2370</v>
+        <v>2317</v>
       </c>
       <c r="C4" t="n">
-        <v>1855</v>
+        <v>4293</v>
       </c>
       <c r="D4" t="n">
-        <v>2133</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1087</v>
+        <v>994</v>
       </c>
       <c r="C5" t="n">
-        <v>1240</v>
+        <v>2539</v>
       </c>
       <c r="D5" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>531</v>
+        <v>756</v>
       </c>
       <c r="D6" t="n">
-        <v>938</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6740</v>
+        <v>5975</v>
       </c>
       <c r="C2" t="n">
-        <v>11762</v>
+        <v>12282</v>
       </c>
       <c r="D2" t="n">
-        <v>31438</v>
+        <v>27949</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3920</v>
+        <v>3386</v>
       </c>
       <c r="C3" t="n">
-        <v>6221</v>
+        <v>5865</v>
       </c>
       <c r="D3" t="n">
-        <v>8037</v>
+        <v>10571</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1743</v>
+        <v>1790</v>
       </c>
       <c r="C4" t="n">
-        <v>3047</v>
+        <v>4328</v>
       </c>
       <c r="D4" t="n">
-        <v>2465</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>909</v>
+        <v>866</v>
       </c>
       <c r="C5" t="n">
-        <v>1148</v>
+        <v>2501</v>
       </c>
       <c r="D5" t="n">
-        <v>1116</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>333</v>
+        <v>292</v>
       </c>
       <c r="C6" t="n">
-        <v>600</v>
+        <v>1114</v>
       </c>
       <c r="D6" t="n">
-        <v>748</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>282</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6989</v>
+        <v>5137</v>
       </c>
       <c r="C2" t="n">
-        <v>9052</v>
+        <v>10061</v>
       </c>
       <c r="D2" t="n">
-        <v>32939</v>
+        <v>22866</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4448</v>
+        <v>3870</v>
       </c>
       <c r="C3" t="n">
-        <v>8206</v>
+        <v>8273</v>
       </c>
       <c r="D3" t="n">
-        <v>11551</v>
+        <v>12712</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2516</v>
+        <v>2247</v>
       </c>
       <c r="C4" t="n">
-        <v>4964</v>
+        <v>5167</v>
       </c>
       <c r="D4" t="n">
-        <v>3566</v>
+        <v>4537</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C5" t="n">
-        <v>2272</v>
+        <v>3518</v>
       </c>
       <c r="D5" t="n">
-        <v>1343</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>585</v>
+        <v>532</v>
       </c>
       <c r="C6" t="n">
-        <v>913</v>
+        <v>1886</v>
       </c>
       <c r="D6" t="n">
-        <v>811</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="C7" t="n">
-        <v>465</v>
+        <v>777</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4848</v>
+        <v>5259</v>
       </c>
       <c r="C2" t="n">
-        <v>5200</v>
+        <v>14889</v>
       </c>
       <c r="D2" t="n">
-        <v>26164</v>
+        <v>21631</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4690</v>
+        <v>3728</v>
       </c>
       <c r="C3" t="n">
-        <v>7496</v>
+        <v>8003</v>
       </c>
       <c r="D3" t="n">
-        <v>14141</v>
+        <v>13421</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2988</v>
+        <v>2597</v>
       </c>
       <c r="C4" t="n">
-        <v>6728</v>
+        <v>6788</v>
       </c>
       <c r="D4" t="n">
-        <v>4956</v>
+        <v>5968</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1629</v>
+        <v>1502</v>
       </c>
       <c r="C5" t="n">
-        <v>3701</v>
+        <v>4297</v>
       </c>
       <c r="D5" t="n">
-        <v>1728</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>811</v>
+        <v>768</v>
       </c>
       <c r="C6" t="n">
-        <v>1645</v>
+        <v>2726</v>
       </c>
       <c r="D6" t="n">
-        <v>888</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>706</v>
+        <v>1352</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>363</v>
+        <v>529</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_46_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_46_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5445</v>
+        <v>941</v>
       </c>
       <c r="C2" t="n">
-        <v>10111</v>
+        <v>3667</v>
       </c>
       <c r="D2" t="n">
-        <v>25382</v>
+        <v>14026</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3629</v>
+        <v>1232</v>
       </c>
       <c r="C3" t="n">
-        <v>9923</v>
+        <v>9488</v>
       </c>
       <c r="D3" t="n">
-        <v>13679</v>
+        <v>14427</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2658</v>
+        <v>666</v>
       </c>
       <c r="C4" t="n">
-        <v>7199</v>
+        <v>12671</v>
       </c>
       <c r="D4" t="n">
-        <v>7017</v>
+        <v>6476</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1756</v>
+        <v>321</v>
       </c>
       <c r="C5" t="n">
-        <v>5451</v>
+        <v>8403</v>
       </c>
       <c r="D5" t="n">
-        <v>2655</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1008</v>
+        <v>157</v>
       </c>
       <c r="C6" t="n">
-        <v>3451</v>
+        <v>3544</v>
       </c>
       <c r="D6" t="n">
-        <v>1118</v>
+        <v>732</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>458</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>1984</v>
+        <v>1089</v>
       </c>
       <c r="D7" t="n">
-        <v>638</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>907</v>
+        <v>370</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>369</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6879</v>
+        <v>1037</v>
       </c>
       <c r="C2" t="n">
-        <v>7793</v>
+        <v>2922</v>
       </c>
       <c r="D2" t="n">
-        <v>31717</v>
+        <v>14965</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3597</v>
+        <v>929</v>
       </c>
       <c r="C3" t="n">
-        <v>8836</v>
+        <v>5835</v>
       </c>
       <c r="D3" t="n">
-        <v>14279</v>
+        <v>13376</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2618</v>
+        <v>791</v>
       </c>
       <c r="C4" t="n">
-        <v>8235</v>
+        <v>10909</v>
       </c>
       <c r="D4" t="n">
-        <v>7759</v>
+        <v>7653</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1889</v>
+        <v>413</v>
       </c>
       <c r="C5" t="n">
-        <v>6126</v>
+        <v>10276</v>
       </c>
       <c r="D5" t="n">
-        <v>3244</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1212</v>
+        <v>206</v>
       </c>
       <c r="C6" t="n">
-        <v>4248</v>
+        <v>5782</v>
       </c>
       <c r="D6" t="n">
-        <v>1313</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>610</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>2596</v>
+        <v>2181</v>
       </c>
       <c r="D7" t="n">
-        <v>702</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>252</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1360</v>
+        <v>669</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>581</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8091</v>
+        <v>579</v>
       </c>
       <c r="C2" t="n">
-        <v>9172</v>
+        <v>1352</v>
       </c>
       <c r="D2" t="n">
-        <v>33514</v>
+        <v>10354</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3942</v>
+        <v>921</v>
       </c>
       <c r="C3" t="n">
-        <v>7493</v>
+        <v>4613</v>
       </c>
       <c r="D3" t="n">
-        <v>15457</v>
+        <v>13232</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2553</v>
+        <v>865</v>
       </c>
       <c r="C4" t="n">
-        <v>8317</v>
+        <v>10080</v>
       </c>
       <c r="D4" t="n">
-        <v>8462</v>
+        <v>8337</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1932</v>
+        <v>413</v>
       </c>
       <c r="C5" t="n">
-        <v>6790</v>
+        <v>11866</v>
       </c>
       <c r="D5" t="n">
-        <v>3721</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1343</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>4909</v>
+        <v>6757</v>
       </c>
       <c r="D6" t="n">
-        <v>1555</v>
+        <v>920</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>752</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>3242</v>
+        <v>1899</v>
       </c>
       <c r="D7" t="n">
-        <v>765</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>341</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1806</v>
+        <v>515</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>857</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>382</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7387</v>
+        <v>614</v>
       </c>
       <c r="C2" t="n">
-        <v>6383</v>
+        <v>11616</v>
       </c>
       <c r="D2" t="n">
-        <v>27553</v>
+        <v>11124</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4626</v>
+        <v>665</v>
       </c>
       <c r="C3" t="n">
-        <v>11740</v>
+        <v>2765</v>
       </c>
       <c r="D3" t="n">
-        <v>16696</v>
+        <v>11951</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1785</v>
+        <v>785</v>
       </c>
       <c r="C4" t="n">
-        <v>10909</v>
+        <v>7342</v>
       </c>
       <c r="D4" t="n">
-        <v>8095</v>
+        <v>8882</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1240</v>
+        <v>524</v>
       </c>
       <c r="C5" t="n">
-        <v>4810</v>
+        <v>10927</v>
       </c>
       <c r="D5" t="n">
-        <v>2524</v>
+        <v>3719</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>694</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>3177</v>
+        <v>8919</v>
       </c>
       <c r="D6" t="n">
-        <v>749</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>1769</v>
+        <v>3887</v>
       </c>
       <c r="D7" t="n">
-        <v>463</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>839</v>
+        <v>1026</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4362</v>
+        <v>325</v>
       </c>
       <c r="C2" t="n">
-        <v>3352</v>
+        <v>5814</v>
       </c>
       <c r="D2" t="n">
-        <v>20249</v>
+        <v>8971</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4945</v>
+        <v>567</v>
       </c>
       <c r="C3" t="n">
-        <v>8526</v>
+        <v>5694</v>
       </c>
       <c r="D3" t="n">
-        <v>17371</v>
+        <v>11201</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2456</v>
+        <v>690</v>
       </c>
       <c r="C4" t="n">
-        <v>11475</v>
+        <v>5511</v>
       </c>
       <c r="D4" t="n">
-        <v>9165</v>
+        <v>9109</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1373</v>
+        <v>575</v>
       </c>
       <c r="C5" t="n">
-        <v>7295</v>
+        <v>9811</v>
       </c>
       <c r="D5" t="n">
-        <v>3215</v>
+        <v>4272</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>813</v>
+        <v>293</v>
       </c>
       <c r="C6" t="n">
-        <v>3920</v>
+        <v>9912</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>295</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>2265</v>
+        <v>5384</v>
       </c>
       <c r="D7" t="n">
-        <v>503</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1116</v>
+        <v>1580</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4934</v>
+        <v>343</v>
       </c>
       <c r="C2" t="n">
-        <v>4520</v>
+        <v>9726</v>
       </c>
       <c r="D2" t="n">
-        <v>27821</v>
+        <v>8135</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3958</v>
+        <v>405</v>
       </c>
       <c r="C3" t="n">
-        <v>5515</v>
+        <v>5099</v>
       </c>
       <c r="D3" t="n">
-        <v>16595</v>
+        <v>10216</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3003</v>
+        <v>561</v>
       </c>
       <c r="C4" t="n">
-        <v>9849</v>
+        <v>5475</v>
       </c>
       <c r="D4" t="n">
-        <v>10225</v>
+        <v>9133</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1611</v>
+        <v>566</v>
       </c>
       <c r="C5" t="n">
-        <v>9029</v>
+        <v>7926</v>
       </c>
       <c r="D5" t="n">
-        <v>4031</v>
+        <v>4792</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>949</v>
+        <v>359</v>
       </c>
       <c r="C6" t="n">
-        <v>5379</v>
+        <v>9789</v>
       </c>
       <c r="D6" t="n">
-        <v>1234</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>431</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>2945</v>
+        <v>7068</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1576</v>
+        <v>2936</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>667</v>
+        <v>782</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2976</v>
+        <v>244</v>
       </c>
       <c r="C2" t="n">
-        <v>2197</v>
+        <v>5525</v>
       </c>
       <c r="D2" t="n">
-        <v>19429</v>
+        <v>5987</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4033</v>
+        <v>552</v>
       </c>
       <c r="C3" t="n">
-        <v>5046</v>
+        <v>6613</v>
       </c>
       <c r="D3" t="n">
-        <v>17390</v>
+        <v>10941</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3290</v>
+        <v>808</v>
       </c>
       <c r="C4" t="n">
-        <v>9258</v>
+        <v>8229</v>
       </c>
       <c r="D4" t="n">
-        <v>11032</v>
+        <v>9304</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1669</v>
+        <v>347</v>
       </c>
       <c r="C5" t="n">
-        <v>10581</v>
+        <v>12848</v>
       </c>
       <c r="D5" t="n">
-        <v>4231</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>766</v>
+        <v>129</v>
       </c>
       <c r="C6" t="n">
-        <v>6230</v>
+        <v>8845</v>
       </c>
       <c r="D6" t="n">
-        <v>1199</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>134</v>
+        <v>51</v>
       </c>
       <c r="C7" t="n">
-        <v>3001</v>
+        <v>2877</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1101</v>
+        <v>766</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2790</v>
+        <v>130</v>
       </c>
       <c r="C2" t="n">
-        <v>5117</v>
+        <v>2785</v>
       </c>
       <c r="D2" t="n">
-        <v>18017</v>
+        <v>5002</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3093</v>
+        <v>369</v>
       </c>
       <c r="C3" t="n">
-        <v>3411</v>
+        <v>5486</v>
       </c>
       <c r="D3" t="n">
-        <v>16510</v>
+        <v>9602</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3121</v>
+        <v>575</v>
       </c>
       <c r="C4" t="n">
-        <v>7164</v>
+        <v>7002</v>
       </c>
       <c r="D4" t="n">
-        <v>11673</v>
+        <v>8800</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2032</v>
+        <v>359</v>
       </c>
       <c r="C5" t="n">
-        <v>9890</v>
+        <v>9507</v>
       </c>
       <c r="D5" t="n">
-        <v>5081</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>993</v>
+        <v>119</v>
       </c>
       <c r="C6" t="n">
-        <v>7990</v>
+        <v>8619</v>
       </c>
       <c r="D6" t="n">
-        <v>1602</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>275</v>
+        <v>37</v>
       </c>
       <c r="C7" t="n">
-        <v>4292</v>
+        <v>3703</v>
       </c>
       <c r="D7" t="n">
-        <v>630</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>1773</v>
+        <v>933</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>538</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>109</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2000</v>
+        <v>97</v>
       </c>
       <c r="C2" t="n">
-        <v>2974</v>
+        <v>9869</v>
       </c>
       <c r="D2" t="n">
-        <v>14568</v>
+        <v>6883</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2633</v>
+        <v>222</v>
       </c>
       <c r="C3" t="n">
-        <v>3724</v>
+        <v>3625</v>
       </c>
       <c r="D3" t="n">
-        <v>15807</v>
+        <v>8278</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2838</v>
+        <v>422</v>
       </c>
       <c r="C4" t="n">
-        <v>5780</v>
+        <v>6070</v>
       </c>
       <c r="D4" t="n">
-        <v>12033</v>
+        <v>8671</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2229</v>
+        <v>408</v>
       </c>
       <c r="C5" t="n">
-        <v>9053</v>
+        <v>8150</v>
       </c>
       <c r="D5" t="n">
-        <v>5720</v>
+        <v>5044</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1149</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>8877</v>
+        <v>8948</v>
       </c>
       <c r="D6" t="n">
-        <v>1881</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>244</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>5418</v>
+        <v>6002</v>
       </c>
       <c r="D7" t="n">
-        <v>701</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>2305</v>
+        <v>2127</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>597</v>
+        <v>533</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2888</v>
+        <v>149</v>
       </c>
       <c r="C2" t="n">
-        <v>17772</v>
+        <v>20541</v>
       </c>
       <c r="D2" t="n">
-        <v>17462</v>
+        <v>10917</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2040</v>
+        <v>145</v>
       </c>
       <c r="C3" t="n">
-        <v>3072</v>
+        <v>5643</v>
       </c>
       <c r="D3" t="n">
-        <v>14681</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2406</v>
+        <v>294</v>
       </c>
       <c r="C4" t="n">
-        <v>4830</v>
+        <v>4793</v>
       </c>
       <c r="D4" t="n">
-        <v>12174</v>
+        <v>8343</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2236</v>
+        <v>377</v>
       </c>
       <c r="C5" t="n">
-        <v>7607</v>
+        <v>7041</v>
       </c>
       <c r="D5" t="n">
-        <v>6279</v>
+        <v>5447</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1372</v>
+        <v>257</v>
       </c>
       <c r="C6" t="n">
-        <v>8870</v>
+        <v>8431</v>
       </c>
       <c r="D6" t="n">
-        <v>2336</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>460</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>6636</v>
+        <v>7269</v>
       </c>
       <c r="D7" t="n">
-        <v>832</v>
+        <v>867</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>3363</v>
+        <v>3721</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1115</v>
+        <v>1157</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4764</v>
+        <v>1967</v>
       </c>
       <c r="C2" t="n">
-        <v>6606</v>
+        <v>24934</v>
       </c>
       <c r="D2" t="n">
-        <v>6521</v>
+        <v>14704</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2111</v>
+        <v>90</v>
       </c>
       <c r="C2" t="n">
-        <v>10521</v>
+        <v>15209</v>
       </c>
       <c r="D2" t="n">
-        <v>12992</v>
+        <v>11134</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2765</v>
+        <v>121</v>
       </c>
       <c r="C3" t="n">
-        <v>6456</v>
+        <v>10318</v>
       </c>
       <c r="D3" t="n">
-        <v>16006</v>
+        <v>7455</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3275</v>
+        <v>207</v>
       </c>
       <c r="C4" t="n">
-        <v>7382</v>
+        <v>4998</v>
       </c>
       <c r="D4" t="n">
-        <v>12259</v>
+        <v>7972</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1288</v>
+        <v>321</v>
       </c>
       <c r="C5" t="n">
-        <v>11874</v>
+        <v>5920</v>
       </c>
       <c r="D5" t="n">
-        <v>5688</v>
+        <v>5618</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>425</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>8067</v>
+        <v>7811</v>
       </c>
       <c r="D6" t="n">
-        <v>1839</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>3295</v>
+        <v>7638</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1092</v>
+        <v>5040</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>318</v>
+        <v>2049</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>594</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7343</v>
+        <v>2461</v>
       </c>
       <c r="C2" t="n">
-        <v>8325</v>
+        <v>16168</v>
       </c>
       <c r="D2" t="n">
-        <v>17779</v>
+        <v>29402</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2025</v>
+        <v>638</v>
       </c>
       <c r="C3" t="n">
-        <v>3382</v>
+        <v>9846</v>
       </c>
       <c r="D3" t="n">
-        <v>1734</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4515</v>
+        <v>1605</v>
       </c>
       <c r="C2" t="n">
-        <v>5773</v>
+        <v>12884</v>
       </c>
       <c r="D2" t="n">
-        <v>15715</v>
+        <v>22780</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3841</v>
+        <v>1298</v>
       </c>
       <c r="C3" t="n">
-        <v>5328</v>
+        <v>11680</v>
       </c>
       <c r="D3" t="n">
-        <v>4301</v>
+        <v>7134</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>913</v>
+        <v>318</v>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>6098</v>
       </c>
       <c r="D4" t="n">
-        <v>1530</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5153</v>
+        <v>1196</v>
       </c>
       <c r="C2" t="n">
-        <v>9049</v>
+        <v>7791</v>
       </c>
       <c r="D2" t="n">
-        <v>26251</v>
+        <v>19354</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3438</v>
+        <v>1194</v>
       </c>
       <c r="C3" t="n">
-        <v>4821</v>
+        <v>10669</v>
       </c>
       <c r="D3" t="n">
-        <v>5817</v>
+        <v>9123</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2008</v>
+        <v>691</v>
       </c>
       <c r="C4" t="n">
-        <v>3853</v>
+        <v>9186</v>
       </c>
       <c r="D4" t="n">
-        <v>2015</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>435</v>
+        <v>181</v>
       </c>
       <c r="C5" t="n">
-        <v>1202</v>
+        <v>3483</v>
       </c>
       <c r="D5" t="n">
-        <v>1201</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>797</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>285</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5908</v>
+        <v>1112</v>
       </c>
       <c r="C2" t="n">
-        <v>8184</v>
+        <v>6416</v>
       </c>
       <c r="D2" t="n">
-        <v>30378</v>
+        <v>26735</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3489</v>
+        <v>988</v>
       </c>
       <c r="C3" t="n">
-        <v>6090</v>
+        <v>7956</v>
       </c>
       <c r="D3" t="n">
-        <v>8513</v>
+        <v>10035</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2317</v>
+        <v>796</v>
       </c>
       <c r="C4" t="n">
-        <v>4293</v>
+        <v>9806</v>
       </c>
       <c r="D4" t="n">
-        <v>2647</v>
+        <v>3713</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>994</v>
+        <v>364</v>
       </c>
       <c r="C5" t="n">
-        <v>2539</v>
+        <v>6421</v>
       </c>
       <c r="D5" t="n">
-        <v>1293</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>255</v>
+        <v>133</v>
       </c>
       <c r="C6" t="n">
-        <v>756</v>
+        <v>1897</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>306</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5975</v>
+        <v>1502</v>
       </c>
       <c r="C2" t="n">
-        <v>12282</v>
+        <v>14964</v>
       </c>
       <c r="D2" t="n">
-        <v>27949</v>
+        <v>30852</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3386</v>
+        <v>862</v>
       </c>
       <c r="C3" t="n">
-        <v>5865</v>
+        <v>6335</v>
       </c>
       <c r="D3" t="n">
-        <v>10571</v>
+        <v>11749</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1790</v>
+        <v>763</v>
       </c>
       <c r="C4" t="n">
-        <v>4328</v>
+        <v>8584</v>
       </c>
       <c r="D4" t="n">
-        <v>3173</v>
+        <v>4692</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>866</v>
+        <v>483</v>
       </c>
       <c r="C5" t="n">
-        <v>2501</v>
+        <v>7944</v>
       </c>
       <c r="D5" t="n">
-        <v>1195</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="C6" t="n">
-        <v>1114</v>
+        <v>4005</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>917</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>1030</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5137</v>
+        <v>1955</v>
       </c>
       <c r="C2" t="n">
-        <v>10061</v>
+        <v>11636</v>
       </c>
       <c r="D2" t="n">
-        <v>22866</v>
+        <v>25204</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3870</v>
+        <v>921</v>
       </c>
       <c r="C3" t="n">
-        <v>8273</v>
+        <v>8908</v>
       </c>
       <c r="D3" t="n">
-        <v>12712</v>
+        <v>13423</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2247</v>
+        <v>690</v>
       </c>
       <c r="C4" t="n">
-        <v>5167</v>
+        <v>7286</v>
       </c>
       <c r="D4" t="n">
-        <v>4537</v>
+        <v>5588</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1185</v>
+        <v>534</v>
       </c>
       <c r="C5" t="n">
-        <v>3518</v>
+        <v>8067</v>
       </c>
       <c r="D5" t="n">
-        <v>1557</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>532</v>
+        <v>290</v>
       </c>
       <c r="C6" t="n">
-        <v>1886</v>
+        <v>5669</v>
       </c>
       <c r="D6" t="n">
-        <v>836</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>777</v>
+        <v>2273</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>289</v>
+        <v>600</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5259</v>
+        <v>1744</v>
       </c>
       <c r="C2" t="n">
-        <v>14889</v>
+        <v>7633</v>
       </c>
       <c r="D2" t="n">
-        <v>21631</v>
+        <v>20477</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3728</v>
+        <v>1192</v>
       </c>
       <c r="C3" t="n">
-        <v>8003</v>
+        <v>13025</v>
       </c>
       <c r="D3" t="n">
-        <v>13421</v>
+        <v>14235</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2597</v>
+        <v>493</v>
       </c>
       <c r="C4" t="n">
-        <v>6788</v>
+        <v>11941</v>
       </c>
       <c r="D4" t="n">
-        <v>5968</v>
+        <v>5136</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1502</v>
+        <v>267</v>
       </c>
       <c r="C5" t="n">
-        <v>4297</v>
+        <v>5555</v>
       </c>
       <c r="D5" t="n">
-        <v>2038</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>768</v>
+        <v>124</v>
       </c>
       <c r="C6" t="n">
-        <v>2726</v>
+        <v>2227</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>1352</v>
+        <v>588</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>441</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>529</v>
+        <v>273</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
